--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_metropolitana.xlsx
@@ -375,766 +375,766 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="C2">
-        <v>449017</v>
+        <v>92.13409541278394</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="C3">
-        <v>365184</v>
+        <v>89.04648718798711</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="C4">
-        <v>313242</v>
+        <v>88.93504350578958</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C5">
-        <v>267935</v>
+        <v>88.68063890684148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="C6">
-        <v>254764</v>
+        <v>87.93312495133428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="C7">
-        <v>178254</v>
+        <v>86.93535035465598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="C8">
-        <v>176302</v>
+        <v>86.86795831571617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="C9">
-        <v>168774</v>
+        <v>86.69430970319149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="C10">
-        <v>161834</v>
+        <v>86.27404317271888</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="C11">
-        <v>142802</v>
+        <v>86.22423945044162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C12">
-        <v>139310</v>
+        <v>85.79952389223209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C13">
-        <v>137347</v>
+        <v>85.53125455919997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="C14">
-        <v>128976</v>
+        <v>85.00358856193102</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="C15">
-        <v>126251</v>
+        <v>84.26030597633581</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C16">
-        <v>123258</v>
+        <v>83.16931598315566</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="C17">
-        <v>109613</v>
+        <v>82.46161590737478</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C18">
-        <v>107120</v>
+        <v>82.20474066999232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="C19">
-        <v>106808</v>
+        <v>81.7933340409723</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="C20">
-        <v>98101</v>
+        <v>81.64305849396072</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C21">
-        <v>96056</v>
+        <v>81.12331081081081</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C22">
-        <v>95321</v>
+        <v>80.41499461681511</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="C23">
-        <v>92705</v>
+        <v>79.8798104703571</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C24">
-        <v>90012</v>
+        <v>79.5216664258139</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C25">
-        <v>89362</v>
+        <v>78.93062306672559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C26">
-        <v>88543</v>
+        <v>78.91155386608038</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C27">
-        <v>86466</v>
+        <v>78.5433139840456</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C28">
-        <v>84668</v>
+        <v>78.51294807590934</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C29">
-        <v>84524</v>
+        <v>78.41717440556057</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C30">
-        <v>83978</v>
+        <v>78.01989309308627</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="C31">
-        <v>79547</v>
+        <v>77.51540572730568</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C32">
-        <v>79051</v>
+        <v>76.56194712632058</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C33">
-        <v>77039</v>
+        <v>76.54395011392253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C34">
-        <v>75582</v>
+        <v>75.80401892360298</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C35">
-        <v>67248</v>
+        <v>74.66511241948868</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C36">
-        <v>67083</v>
+        <v>74.54331003135698</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C37">
-        <v>63791</v>
+        <v>73.43049932523617</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C38">
-        <v>62517</v>
+        <v>72.94393870741854</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C39">
-        <v>60585</v>
+        <v>72.50243659707115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C40">
-        <v>48740</v>
+        <v>72.05398366283887</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C41">
-        <v>38261</v>
+        <v>70.59671329463625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C42">
-        <v>36279</v>
+        <v>67.14606322753994</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C43">
-        <v>34927</v>
+        <v>66.94406688379965</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C44">
-        <v>32762</v>
+        <v>62.21812578027465</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C45">
-        <v>30823</v>
+        <v>60.70794269624679</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C46">
-        <v>27206</v>
+        <v>58.70915848449548</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C47">
-        <v>25912</v>
+        <v>41.73861656317759</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C48">
-        <v>14969</v>
+        <v>40.99758907045272</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C49">
-        <v>14058</v>
+        <v>33.22770028301109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C50">
-        <v>13344</v>
+        <v>31.60276734942649</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C51">
-        <v>9605</v>
+        <v>26.3909255585267</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C52">
-        <v>6912</v>
+        <v>15.46449100686075</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
